--- a/SantanderCS/doc/describe_summary_lkj.xlsx
+++ b/SantanderCS/doc/describe_summary_lkj.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AFFFA4F7-C832-4E36-B3AF-7AC1FFACF7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FBAB19-3938-4C49-A8E6-14E670E971CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{052BFD95-ADC5-4D7C-BDBD-705BDEF23884}"/>
   </bookViews>
@@ -16,12 +16,23 @@
     <sheet name="describe_summary" sheetId="1" r:id="rId1"/>
     <sheet name="LKJ" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="396">
   <si>
     <t>ID</t>
   </si>
@@ -78,9 +89,6 @@
   </si>
   <si>
     <t>imp_op_var39_ult1</t>
-  </si>
-  <si>
-    <t>imp_sal_var16_ult1</t>
   </si>
   <si>
     <t>ind_var1_0</t>
@@ -1164,6 +1172,67 @@
   </si>
   <si>
     <t>상한값</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_var44_0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>파악한 특성</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제여부(Y/N)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>fillna할 값</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>imp_sal_var16_ult1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>`</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래횟수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_var41</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>na_Sum</t>
+  </si>
+  <si>
+    <t>nUnique</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>modeFreq</t>
+  </si>
+  <si>
+    <t>modeFreqRate</t>
+  </si>
+  <si>
+    <t>zero_count</t>
+  </si>
+  <si>
+    <t>zero_count_rate</t>
+  </si>
+  <si>
+    <t>거래횟수 - zero_count &gt; 95% 이상</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1332,7 +1401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1510,6 +1579,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1757,7 +1832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1772,6 +1847,24 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2131,7 +2224,9 @@
   <dimension ref="A1:NH9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="149" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="20" width="9" customWidth="1"/>
+    <col min="21" max="21" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="149" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:372" x14ac:dyDescent="0.3">
@@ -2193,1065 +2288,1065 @@
         <v>18</v>
       </c>
       <c r="U1" t="s">
+        <v>384</v>
+      </c>
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>87</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>88</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>89</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>90</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>91</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>92</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>93</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>94</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>95</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>96</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>97</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>98</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>99</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>100</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>101</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>102</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>103</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>104</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>105</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>106</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>107</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>108</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>109</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>110</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DJ1" t="s">
         <v>111</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DK1" t="s">
         <v>112</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DL1" t="s">
         <v>113</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DM1" t="s">
         <v>114</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DN1" t="s">
         <v>115</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DO1" t="s">
         <v>116</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DP1" t="s">
         <v>117</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DQ1" t="s">
         <v>118</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DR1" t="s">
         <v>119</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DS1" t="s">
         <v>120</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="DT1" t="s">
         <v>121</v>
       </c>
-      <c r="DT1" t="s">
+      <c r="DU1" t="s">
         <v>122</v>
       </c>
-      <c r="DU1" t="s">
+      <c r="DV1" t="s">
         <v>123</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="DW1" t="s">
         <v>124</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="DX1" t="s">
         <v>125</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DY1" t="s">
         <v>126</v>
       </c>
-      <c r="DY1" t="s">
+      <c r="DZ1" t="s">
         <v>127</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EA1" t="s">
         <v>128</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EB1" t="s">
         <v>129</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="EC1" t="s">
         <v>130</v>
       </c>
-      <c r="EC1" t="s">
+      <c r="ED1" t="s">
         <v>131</v>
       </c>
-      <c r="ED1" t="s">
+      <c r="EE1" t="s">
         <v>132</v>
       </c>
-      <c r="EE1" t="s">
+      <c r="EF1" t="s">
         <v>133</v>
       </c>
-      <c r="EF1" t="s">
+      <c r="EG1" t="s">
         <v>134</v>
       </c>
-      <c r="EG1" t="s">
+      <c r="EH1" t="s">
         <v>135</v>
       </c>
-      <c r="EH1" t="s">
+      <c r="EI1" t="s">
         <v>136</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="EJ1" t="s">
         <v>137</v>
       </c>
-      <c r="EJ1" t="s">
+      <c r="EK1" t="s">
         <v>138</v>
       </c>
-      <c r="EK1" t="s">
+      <c r="EL1" t="s">
         <v>139</v>
       </c>
-      <c r="EL1" t="s">
+      <c r="EM1" t="s">
         <v>140</v>
       </c>
-      <c r="EM1" t="s">
+      <c r="EN1" t="s">
         <v>141</v>
       </c>
-      <c r="EN1" t="s">
+      <c r="EO1" t="s">
         <v>142</v>
       </c>
-      <c r="EO1" t="s">
+      <c r="EP1" t="s">
         <v>143</v>
       </c>
-      <c r="EP1" t="s">
+      <c r="EQ1" t="s">
         <v>144</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="ER1" t="s">
         <v>145</v>
       </c>
-      <c r="ER1" t="s">
+      <c r="ES1" t="s">
         <v>146</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="ET1" t="s">
         <v>147</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EU1" t="s">
         <v>148</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EV1" t="s">
         <v>149</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EW1" t="s">
         <v>150</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="EX1" t="s">
         <v>151</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="EY1" t="s">
         <v>152</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="EZ1" t="s">
         <v>153</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FA1" t="s">
         <v>154</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FB1" t="s">
         <v>155</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FC1" t="s">
         <v>156</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FD1" t="s">
         <v>157</v>
       </c>
-      <c r="FD1" t="s">
+      <c r="FE1" t="s">
         <v>158</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FF1" t="s">
         <v>159</v>
       </c>
-      <c r="FF1" t="s">
+      <c r="FG1" t="s">
         <v>160</v>
       </c>
-      <c r="FG1" t="s">
+      <c r="FH1" t="s">
         <v>161</v>
       </c>
-      <c r="FH1" t="s">
+      <c r="FI1" t="s">
         <v>162</v>
       </c>
-      <c r="FI1" t="s">
+      <c r="FJ1" t="s">
         <v>163</v>
       </c>
-      <c r="FJ1" t="s">
+      <c r="FK1" t="s">
         <v>164</v>
       </c>
-      <c r="FK1" t="s">
+      <c r="FL1" t="s">
         <v>165</v>
       </c>
-      <c r="FL1" t="s">
+      <c r="FM1" t="s">
         <v>166</v>
       </c>
-      <c r="FM1" t="s">
+      <c r="FN1" t="s">
         <v>167</v>
       </c>
-      <c r="FN1" t="s">
+      <c r="FO1" t="s">
         <v>168</v>
       </c>
-      <c r="FO1" t="s">
+      <c r="FP1" t="s">
         <v>169</v>
       </c>
-      <c r="FP1" t="s">
+      <c r="FQ1" t="s">
         <v>170</v>
       </c>
-      <c r="FQ1" t="s">
+      <c r="FR1" t="s">
         <v>171</v>
       </c>
-      <c r="FR1" t="s">
+      <c r="FS1" t="s">
         <v>172</v>
       </c>
-      <c r="FS1" t="s">
+      <c r="FT1" t="s">
         <v>173</v>
       </c>
-      <c r="FT1" t="s">
+      <c r="FU1" t="s">
         <v>174</v>
       </c>
-      <c r="FU1" t="s">
+      <c r="FV1" t="s">
         <v>175</v>
       </c>
-      <c r="FV1" t="s">
+      <c r="FW1" t="s">
         <v>176</v>
       </c>
-      <c r="FW1" t="s">
+      <c r="FX1" t="s">
         <v>177</v>
       </c>
-      <c r="FX1" t="s">
+      <c r="FY1" t="s">
         <v>178</v>
       </c>
-      <c r="FY1" t="s">
+      <c r="FZ1" t="s">
         <v>179</v>
       </c>
-      <c r="FZ1" t="s">
+      <c r="GA1" t="s">
         <v>180</v>
       </c>
-      <c r="GA1" t="s">
+      <c r="GB1" t="s">
         <v>181</v>
       </c>
-      <c r="GB1" t="s">
+      <c r="GC1" t="s">
         <v>182</v>
       </c>
-      <c r="GC1" t="s">
+      <c r="GD1" t="s">
         <v>183</v>
       </c>
-      <c r="GD1" t="s">
+      <c r="GE1" t="s">
         <v>184</v>
       </c>
-      <c r="GE1" t="s">
+      <c r="GF1" t="s">
         <v>185</v>
       </c>
-      <c r="GF1" t="s">
+      <c r="GG1" t="s">
         <v>186</v>
       </c>
-      <c r="GG1" t="s">
+      <c r="GH1" t="s">
         <v>187</v>
       </c>
-      <c r="GH1" t="s">
+      <c r="GI1" t="s">
         <v>188</v>
       </c>
-      <c r="GI1" t="s">
+      <c r="GJ1" t="s">
         <v>189</v>
       </c>
-      <c r="GJ1" t="s">
+      <c r="GK1" t="s">
         <v>190</v>
       </c>
-      <c r="GK1" t="s">
+      <c r="GL1" t="s">
         <v>191</v>
       </c>
-      <c r="GL1" t="s">
+      <c r="GM1" t="s">
         <v>192</v>
       </c>
-      <c r="GM1" t="s">
+      <c r="GN1" t="s">
         <v>193</v>
       </c>
-      <c r="GN1" t="s">
+      <c r="GO1" t="s">
         <v>194</v>
       </c>
-      <c r="GO1" t="s">
+      <c r="GP1" t="s">
         <v>195</v>
       </c>
-      <c r="GP1" t="s">
+      <c r="GQ1" t="s">
         <v>196</v>
       </c>
-      <c r="GQ1" t="s">
+      <c r="GR1" t="s">
         <v>197</v>
       </c>
-      <c r="GR1" t="s">
+      <c r="GS1" t="s">
         <v>198</v>
       </c>
-      <c r="GS1" t="s">
+      <c r="GT1" t="s">
         <v>199</v>
       </c>
-      <c r="GT1" t="s">
+      <c r="GU1" t="s">
         <v>200</v>
       </c>
-      <c r="GU1" t="s">
+      <c r="GV1" t="s">
         <v>201</v>
       </c>
-      <c r="GV1" t="s">
+      <c r="GW1" t="s">
         <v>202</v>
       </c>
-      <c r="GW1" t="s">
+      <c r="GX1" t="s">
         <v>203</v>
       </c>
-      <c r="GX1" t="s">
+      <c r="GY1" t="s">
         <v>204</v>
       </c>
-      <c r="GY1" t="s">
+      <c r="GZ1" t="s">
         <v>205</v>
       </c>
-      <c r="GZ1" t="s">
+      <c r="HA1" t="s">
         <v>206</v>
       </c>
-      <c r="HA1" t="s">
+      <c r="HB1" t="s">
         <v>207</v>
       </c>
-      <c r="HB1" t="s">
+      <c r="HC1" t="s">
         <v>208</v>
       </c>
-      <c r="HC1" t="s">
+      <c r="HD1" t="s">
         <v>209</v>
       </c>
-      <c r="HD1" t="s">
+      <c r="HE1" t="s">
         <v>210</v>
       </c>
-      <c r="HE1" t="s">
+      <c r="HF1" t="s">
         <v>211</v>
       </c>
-      <c r="HF1" t="s">
+      <c r="HG1" t="s">
         <v>212</v>
       </c>
-      <c r="HG1" t="s">
+      <c r="HH1" t="s">
         <v>213</v>
       </c>
-      <c r="HH1" t="s">
+      <c r="HI1" t="s">
         <v>214</v>
       </c>
-      <c r="HI1" t="s">
+      <c r="HJ1" t="s">
         <v>215</v>
       </c>
-      <c r="HJ1" t="s">
+      <c r="HK1" t="s">
         <v>216</v>
       </c>
-      <c r="HK1" t="s">
+      <c r="HL1" t="s">
         <v>217</v>
       </c>
-      <c r="HL1" t="s">
+      <c r="HM1" t="s">
         <v>218</v>
       </c>
-      <c r="HM1" t="s">
+      <c r="HN1" t="s">
         <v>219</v>
       </c>
-      <c r="HN1" t="s">
+      <c r="HO1" t="s">
         <v>220</v>
       </c>
-      <c r="HO1" t="s">
+      <c r="HP1" t="s">
         <v>221</v>
       </c>
-      <c r="HP1" t="s">
+      <c r="HQ1" t="s">
         <v>222</v>
       </c>
-      <c r="HQ1" t="s">
+      <c r="HR1" t="s">
         <v>223</v>
       </c>
-      <c r="HR1" t="s">
+      <c r="HS1" t="s">
         <v>224</v>
       </c>
-      <c r="HS1" t="s">
+      <c r="HT1" t="s">
         <v>225</v>
       </c>
-      <c r="HT1" t="s">
+      <c r="HU1" t="s">
         <v>226</v>
       </c>
-      <c r="HU1" t="s">
+      <c r="HV1" t="s">
         <v>227</v>
       </c>
-      <c r="HV1" t="s">
+      <c r="HW1" t="s">
         <v>228</v>
       </c>
-      <c r="HW1" t="s">
+      <c r="HX1" t="s">
         <v>229</v>
       </c>
-      <c r="HX1" t="s">
+      <c r="HY1" t="s">
         <v>230</v>
       </c>
-      <c r="HY1" t="s">
+      <c r="HZ1" t="s">
         <v>231</v>
       </c>
-      <c r="HZ1" t="s">
+      <c r="IA1" t="s">
         <v>232</v>
       </c>
-      <c r="IA1" t="s">
+      <c r="IB1" t="s">
         <v>233</v>
       </c>
-      <c r="IB1" t="s">
+      <c r="IC1" t="s">
         <v>234</v>
       </c>
-      <c r="IC1" t="s">
+      <c r="ID1" t="s">
         <v>235</v>
       </c>
-      <c r="ID1" t="s">
+      <c r="IE1" t="s">
         <v>236</v>
       </c>
-      <c r="IE1" t="s">
+      <c r="IF1" t="s">
         <v>237</v>
       </c>
-      <c r="IF1" t="s">
+      <c r="IG1" t="s">
         <v>238</v>
       </c>
-      <c r="IG1" t="s">
+      <c r="IH1" t="s">
         <v>239</v>
       </c>
-      <c r="IH1" t="s">
+      <c r="II1" t="s">
         <v>240</v>
       </c>
-      <c r="II1" t="s">
+      <c r="IJ1" t="s">
         <v>241</v>
       </c>
-      <c r="IJ1" t="s">
+      <c r="IK1" t="s">
         <v>242</v>
       </c>
-      <c r="IK1" t="s">
+      <c r="IL1" t="s">
         <v>243</v>
       </c>
-      <c r="IL1" t="s">
+      <c r="IM1" t="s">
         <v>244</v>
       </c>
-      <c r="IM1" t="s">
+      <c r="IN1" t="s">
         <v>245</v>
       </c>
-      <c r="IN1" t="s">
+      <c r="IO1" t="s">
         <v>246</v>
       </c>
-      <c r="IO1" t="s">
+      <c r="IP1" t="s">
         <v>247</v>
       </c>
-      <c r="IP1" t="s">
+      <c r="IQ1" t="s">
         <v>248</v>
       </c>
-      <c r="IQ1" t="s">
+      <c r="IR1" t="s">
         <v>249</v>
       </c>
-      <c r="IR1" t="s">
+      <c r="IS1" t="s">
         <v>250</v>
       </c>
-      <c r="IS1" t="s">
+      <c r="IT1" t="s">
         <v>251</v>
       </c>
-      <c r="IT1" t="s">
+      <c r="IU1" t="s">
         <v>252</v>
       </c>
-      <c r="IU1" t="s">
+      <c r="IV1" t="s">
         <v>253</v>
       </c>
-      <c r="IV1" t="s">
+      <c r="IW1" t="s">
         <v>254</v>
       </c>
-      <c r="IW1" t="s">
+      <c r="IX1" t="s">
         <v>255</v>
       </c>
-      <c r="IX1" t="s">
+      <c r="IY1" t="s">
         <v>256</v>
       </c>
-      <c r="IY1" t="s">
+      <c r="IZ1" t="s">
         <v>257</v>
       </c>
-      <c r="IZ1" t="s">
+      <c r="JA1" t="s">
         <v>258</v>
       </c>
-      <c r="JA1" t="s">
+      <c r="JB1" t="s">
         <v>259</v>
       </c>
-      <c r="JB1" t="s">
+      <c r="JC1" t="s">
         <v>260</v>
       </c>
-      <c r="JC1" t="s">
+      <c r="JD1" t="s">
         <v>261</v>
       </c>
-      <c r="JD1" t="s">
+      <c r="JE1" t="s">
         <v>262</v>
       </c>
-      <c r="JE1" t="s">
+      <c r="JF1" t="s">
         <v>263</v>
       </c>
-      <c r="JF1" t="s">
+      <c r="JG1" t="s">
         <v>264</v>
       </c>
-      <c r="JG1" t="s">
+      <c r="JH1" t="s">
         <v>265</v>
       </c>
-      <c r="JH1" t="s">
+      <c r="JI1" t="s">
         <v>266</v>
       </c>
-      <c r="JI1" t="s">
+      <c r="JJ1" t="s">
         <v>267</v>
       </c>
-      <c r="JJ1" t="s">
+      <c r="JK1" t="s">
         <v>268</v>
       </c>
-      <c r="JK1" t="s">
+      <c r="JL1" t="s">
         <v>269</v>
       </c>
-      <c r="JL1" t="s">
+      <c r="JM1" t="s">
         <v>270</v>
       </c>
-      <c r="JM1" t="s">
+      <c r="JN1" t="s">
         <v>271</v>
       </c>
-      <c r="JN1" t="s">
+      <c r="JO1" t="s">
         <v>272</v>
       </c>
-      <c r="JO1" t="s">
+      <c r="JP1" t="s">
         <v>273</v>
       </c>
-      <c r="JP1" t="s">
+      <c r="JQ1" t="s">
         <v>274</v>
       </c>
-      <c r="JQ1" t="s">
+      <c r="JR1" t="s">
         <v>275</v>
       </c>
-      <c r="JR1" t="s">
+      <c r="JS1" t="s">
         <v>276</v>
       </c>
-      <c r="JS1" t="s">
+      <c r="JT1" t="s">
         <v>277</v>
       </c>
-      <c r="JT1" t="s">
+      <c r="JU1" t="s">
         <v>278</v>
       </c>
-      <c r="JU1" t="s">
+      <c r="JV1" t="s">
         <v>279</v>
       </c>
-      <c r="JV1" t="s">
+      <c r="JW1" t="s">
         <v>280</v>
       </c>
-      <c r="JW1" t="s">
+      <c r="JX1" t="s">
         <v>281</v>
       </c>
-      <c r="JX1" t="s">
+      <c r="JY1" t="s">
         <v>282</v>
       </c>
-      <c r="JY1" t="s">
+      <c r="JZ1" t="s">
         <v>283</v>
       </c>
-      <c r="JZ1" t="s">
+      <c r="KA1" t="s">
         <v>284</v>
       </c>
-      <c r="KA1" t="s">
+      <c r="KB1" t="s">
         <v>285</v>
       </c>
-      <c r="KB1" t="s">
+      <c r="KC1" t="s">
         <v>286</v>
       </c>
-      <c r="KC1" t="s">
+      <c r="KD1" t="s">
         <v>287</v>
       </c>
-      <c r="KD1" t="s">
+      <c r="KE1" t="s">
         <v>288</v>
       </c>
-      <c r="KE1" t="s">
+      <c r="KF1" t="s">
         <v>289</v>
       </c>
-      <c r="KF1" t="s">
+      <c r="KG1" t="s">
         <v>290</v>
       </c>
-      <c r="KG1" t="s">
+      <c r="KH1" t="s">
         <v>291</v>
       </c>
-      <c r="KH1" t="s">
+      <c r="KI1" t="s">
         <v>292</v>
       </c>
-      <c r="KI1" t="s">
+      <c r="KJ1" t="s">
         <v>293</v>
       </c>
-      <c r="KJ1" t="s">
+      <c r="KK1" t="s">
         <v>294</v>
       </c>
-      <c r="KK1" t="s">
+      <c r="KL1" t="s">
         <v>295</v>
       </c>
-      <c r="KL1" t="s">
+      <c r="KM1" t="s">
         <v>296</v>
       </c>
-      <c r="KM1" t="s">
+      <c r="KN1" t="s">
         <v>297</v>
       </c>
-      <c r="KN1" t="s">
+      <c r="KO1" t="s">
         <v>298</v>
       </c>
-      <c r="KO1" t="s">
+      <c r="KP1" t="s">
         <v>299</v>
       </c>
-      <c r="KP1" t="s">
+      <c r="KQ1" t="s">
         <v>300</v>
       </c>
-      <c r="KQ1" t="s">
+      <c r="KR1" t="s">
         <v>301</v>
       </c>
-      <c r="KR1" t="s">
+      <c r="KS1" t="s">
         <v>302</v>
       </c>
-      <c r="KS1" t="s">
+      <c r="KT1" t="s">
         <v>303</v>
       </c>
-      <c r="KT1" t="s">
+      <c r="KU1" t="s">
         <v>304</v>
       </c>
-      <c r="KU1" t="s">
+      <c r="KV1" t="s">
         <v>305</v>
       </c>
-      <c r="KV1" t="s">
+      <c r="KW1" t="s">
         <v>306</v>
       </c>
-      <c r="KW1" t="s">
+      <c r="KX1" t="s">
         <v>307</v>
       </c>
-      <c r="KX1" t="s">
+      <c r="KY1" t="s">
         <v>308</v>
       </c>
-      <c r="KY1" t="s">
+      <c r="KZ1" t="s">
         <v>309</v>
       </c>
-      <c r="KZ1" t="s">
+      <c r="LA1" t="s">
         <v>310</v>
       </c>
-      <c r="LA1" t="s">
+      <c r="LB1" t="s">
         <v>311</v>
       </c>
-      <c r="LB1" t="s">
+      <c r="LC1" t="s">
         <v>312</v>
       </c>
-      <c r="LC1" t="s">
+      <c r="LD1" t="s">
         <v>313</v>
       </c>
-      <c r="LD1" t="s">
+      <c r="LE1" t="s">
         <v>314</v>
       </c>
-      <c r="LE1" t="s">
+      <c r="LF1" t="s">
         <v>315</v>
       </c>
-      <c r="LF1" t="s">
+      <c r="LG1" t="s">
         <v>316</v>
       </c>
-      <c r="LG1" t="s">
+      <c r="LH1" t="s">
         <v>317</v>
       </c>
-      <c r="LH1" t="s">
+      <c r="LI1" t="s">
         <v>318</v>
       </c>
-      <c r="LI1" t="s">
+      <c r="LJ1" t="s">
         <v>319</v>
       </c>
-      <c r="LJ1" t="s">
+      <c r="LK1" t="s">
         <v>320</v>
       </c>
-      <c r="LK1" t="s">
+      <c r="LL1" t="s">
         <v>321</v>
       </c>
-      <c r="LL1" t="s">
+      <c r="LM1" t="s">
         <v>322</v>
       </c>
-      <c r="LM1" t="s">
+      <c r="LN1" t="s">
         <v>323</v>
       </c>
-      <c r="LN1" t="s">
+      <c r="LO1" t="s">
         <v>324</v>
       </c>
-      <c r="LO1" t="s">
+      <c r="LP1" t="s">
         <v>325</v>
       </c>
-      <c r="LP1" t="s">
+      <c r="LQ1" t="s">
         <v>326</v>
       </c>
-      <c r="LQ1" t="s">
+      <c r="LR1" t="s">
         <v>327</v>
       </c>
-      <c r="LR1" t="s">
+      <c r="LS1" t="s">
         <v>328</v>
       </c>
-      <c r="LS1" t="s">
+      <c r="LT1" t="s">
         <v>329</v>
       </c>
-      <c r="LT1" t="s">
+      <c r="LU1" t="s">
         <v>330</v>
       </c>
-      <c r="LU1" t="s">
+      <c r="LV1" t="s">
         <v>331</v>
       </c>
-      <c r="LV1" t="s">
+      <c r="LW1" t="s">
         <v>332</v>
       </c>
-      <c r="LW1" t="s">
+      <c r="LX1" t="s">
         <v>333</v>
       </c>
-      <c r="LX1" t="s">
+      <c r="LY1" t="s">
         <v>334</v>
       </c>
-      <c r="LY1" t="s">
+      <c r="LZ1" t="s">
         <v>335</v>
       </c>
-      <c r="LZ1" t="s">
+      <c r="MA1" t="s">
         <v>336</v>
       </c>
-      <c r="MA1" t="s">
+      <c r="MB1" t="s">
         <v>337</v>
       </c>
-      <c r="MB1" t="s">
+      <c r="MC1" t="s">
         <v>338</v>
       </c>
-      <c r="MC1" t="s">
+      <c r="MD1" t="s">
         <v>339</v>
       </c>
-      <c r="MD1" t="s">
+      <c r="ME1" t="s">
         <v>340</v>
       </c>
-      <c r="ME1" t="s">
+      <c r="MF1" t="s">
         <v>341</v>
       </c>
-      <c r="MF1" t="s">
+      <c r="MG1" t="s">
         <v>342</v>
       </c>
-      <c r="MG1" t="s">
+      <c r="MH1" t="s">
         <v>343</v>
       </c>
-      <c r="MH1" t="s">
+      <c r="MI1" t="s">
         <v>344</v>
       </c>
-      <c r="MI1" t="s">
+      <c r="MJ1" t="s">
         <v>345</v>
       </c>
-      <c r="MJ1" t="s">
+      <c r="MK1" t="s">
         <v>346</v>
       </c>
-      <c r="MK1" t="s">
+      <c r="ML1" t="s">
         <v>347</v>
       </c>
-      <c r="ML1" t="s">
+      <c r="MM1" t="s">
         <v>348</v>
       </c>
-      <c r="MM1" t="s">
+      <c r="MN1" t="s">
         <v>349</v>
       </c>
-      <c r="MN1" t="s">
+      <c r="MO1" t="s">
         <v>350</v>
       </c>
-      <c r="MO1" t="s">
+      <c r="MP1" t="s">
         <v>351</v>
       </c>
-      <c r="MP1" t="s">
+      <c r="MQ1" t="s">
         <v>352</v>
       </c>
-      <c r="MQ1" t="s">
+      <c r="MR1" t="s">
         <v>353</v>
       </c>
-      <c r="MR1" t="s">
+      <c r="MS1" t="s">
         <v>354</v>
       </c>
-      <c r="MS1" t="s">
+      <c r="MT1" t="s">
         <v>355</v>
       </c>
-      <c r="MT1" t="s">
+      <c r="MU1" t="s">
         <v>356</v>
       </c>
-      <c r="MU1" t="s">
+      <c r="MV1" t="s">
         <v>357</v>
       </c>
-      <c r="MV1" t="s">
+      <c r="MW1" t="s">
         <v>358</v>
       </c>
-      <c r="MW1" t="s">
+      <c r="MX1" t="s">
         <v>359</v>
       </c>
-      <c r="MX1" t="s">
+      <c r="MY1" t="s">
         <v>360</v>
       </c>
-      <c r="MY1" t="s">
+      <c r="MZ1" t="s">
         <v>361</v>
       </c>
-      <c r="MZ1" t="s">
+      <c r="NA1" t="s">
         <v>362</v>
       </c>
-      <c r="NA1" t="s">
+      <c r="NB1" t="s">
         <v>363</v>
       </c>
-      <c r="NB1" t="s">
+      <c r="NC1" t="s">
         <v>364</v>
       </c>
-      <c r="NC1" t="s">
+      <c r="ND1" t="s">
         <v>365</v>
       </c>
-      <c r="ND1" t="s">
+      <c r="NE1" t="s">
         <v>366</v>
       </c>
-      <c r="NE1" t="s">
+      <c r="NF1" t="s">
         <v>367</v>
       </c>
-      <c r="NF1" t="s">
+      <c r="NG1" t="s">
         <v>368</v>
       </c>
-      <c r="NG1" t="s">
+      <c r="NH1" t="s">
         <v>369</v>
       </c>
-      <c r="NH1" t="s">
+    </row>
+    <row r="2" spans="1:372" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>370</v>
-      </c>
-    </row>
-    <row r="2" spans="1:372" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>371</v>
       </c>
       <c r="B2">
         <v>76020</v>
@@ -4369,7 +4464,7 @@
     </row>
     <row r="3" spans="1:372" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B3">
         <v>75964.050719999999</v>
@@ -5487,7 +5582,7 @@
     </row>
     <row r="4" spans="1:372" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B4">
         <v>43781.947379999998</v>
@@ -6605,7 +6700,7 @@
     </row>
     <row r="5" spans="1:372" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -11077,7 +11172,7 @@
     </row>
     <row r="9" spans="1:372" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B9">
         <v>151838</v>
@@ -12201,14 +12296,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A1D2B3-40A0-4675-B96B-40D64E86AEC3}">
-  <dimension ref="A1:BW15"/>
+  <dimension ref="A1:BW27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
+    <col min="1" max="1" width="16.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.125" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="15" width="12.75" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.625" bestFit="1" customWidth="1"/>
@@ -12244,231 +12339,231 @@
   <sheetData>
     <row r="1" spans="1:75" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
         <v>148</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>149</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>150</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>151</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>152</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>153</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>154</v>
       </c>
-      <c r="I1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="K1" t="s">
         <v>156</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>157</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>158</v>
       </c>
-      <c r="M1" t="s">
-        <v>159</v>
-      </c>
       <c r="N1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O1" t="s">
         <v>160</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>161</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>162</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>163</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>164</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>165</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>166</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>167</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>168</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>169</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>170</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>171</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>172</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>173</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>174</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>175</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>176</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>177</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>178</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>179</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>180</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>181</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>182</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>183</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>184</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>185</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>186</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>187</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>188</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>189</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>190</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>191</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>192</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>193</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>194</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>195</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>196</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>197</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>198</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>199</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>200</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>201</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>202</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>203</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>204</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>205</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>206</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>207</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>208</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>209</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>210</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>211</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>212</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>213</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>214</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>215</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>216</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>217</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>218</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>219</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>220</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B2">
         <v>76020</v>
@@ -12494,7 +12589,7 @@
       <c r="I2">
         <v>76020</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="5">
         <v>76020</v>
       </c>
       <c r="K2">
@@ -12695,7 +12790,7 @@
     </row>
     <row r="3" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B3">
         <v>3.299368587</v>
@@ -12721,7 +12816,7 @@
       <c r="I3">
         <v>2.699250197</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
       <c r="K3">
@@ -12922,7 +13017,7 @@
     </row>
     <row r="4" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B4">
         <v>2.8682166269999998</v>
@@ -12948,7 +13043,7 @@
       <c r="I4">
         <v>1.105296729</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>0</v>
       </c>
       <c r="K4">
@@ -13149,7 +13244,7 @@
     </row>
     <row r="5" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -13175,7 +13270,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="5">
         <v>0</v>
       </c>
       <c r="K5">
@@ -13402,7 +13497,7 @@
       <c r="I6">
         <v>3</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="5">
         <v>0</v>
       </c>
       <c r="K6">
@@ -13629,7 +13724,7 @@
       <c r="I7">
         <v>3</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="5">
         <v>0</v>
       </c>
       <c r="K7">
@@ -13856,7 +13951,7 @@
       <c r="I8">
         <v>3</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8">
@@ -14057,7 +14152,7 @@
     </row>
     <row r="9" spans="1:75" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B9">
         <v>36</v>
@@ -14083,7 +14178,7 @@
       <c r="I9">
         <v>33</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="5">
         <v>0</v>
       </c>
       <c r="K9">
@@ -14282,9 +14377,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:75" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:75" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B12">
         <f>B8-B6</f>
@@ -14318,7 +14415,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14583,9 +14680,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B13">
         <f>B6-(1.5*B12)</f>
@@ -14619,7 +14716,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -14884,9 +14981,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B14">
         <f>B8+(1.5*B12)</f>
@@ -14920,7 +15017,7 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="5">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -15185,16 +15282,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B15" t="b">
-        <f>OR(B3 &lt; B13, B9 &gt;B14 )</f>
+        <f>OR(B5 &lt; B13, B9 &gt;B14 )</f>
         <v>1</v>
       </c>
       <c r="C15" t="b">
-        <f t="shared" ref="C15:BN15" si="6">OR(C3 &lt; C13, C9 &gt;C14 )</f>
+        <f t="shared" ref="C15:BN15" si="6">OR(C5 &lt; C13, C9 &gt;C14 )</f>
         <v>1</v>
       </c>
       <c r="D15" t="b">
@@ -15450,7 +15547,7 @@
         <v>1</v>
       </c>
       <c r="BO15" t="b">
-        <f t="shared" ref="BO15:BW15" si="7">OR(BO3 &lt; BO13, BO9 &gt;BO14 )</f>
+        <f t="shared" ref="BO15:BW15" si="7">OR(BO5 &lt; BO13, BO9 &gt;BO14 )</f>
         <v>1</v>
       </c>
       <c r="BP15" t="b">
@@ -15484,6 +15581,2276 @@
       <c r="BW15" t="b">
         <f t="shared" si="7"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:75" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:75" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AI17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AJ17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AM17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AN17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AO17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AP17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AQ17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AR17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AT17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AU17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AW17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AX17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AY17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="AZ17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BA17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BB17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BC17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BD17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BE17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BF17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BG17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BH17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BI17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BJ17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BK17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BL17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BM17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BN17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BO17" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="BP17" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:75" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="P18" s="7"/>
+    </row>
+    <row r="19" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B19" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AY19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BD19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BM19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BO19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BQ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BU19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV19" t="b">
+        <v>1</v>
+      </c>
+      <c r="BW19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>6244</v>
+      </c>
+      <c r="C20">
+        <v>3568</v>
+      </c>
+      <c r="D20">
+        <v>4961</v>
+      </c>
+      <c r="E20">
+        <v>4961</v>
+      </c>
+      <c r="F20">
+        <v>11007</v>
+      </c>
+      <c r="G20">
+        <v>868</v>
+      </c>
+      <c r="H20">
+        <v>283</v>
+      </c>
+      <c r="I20">
+        <v>10622</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>283</v>
+      </c>
+      <c r="L20">
+        <v>5778</v>
+      </c>
+      <c r="M20">
+        <v>36</v>
+      </c>
+      <c r="N20">
+        <v>143</v>
+      </c>
+      <c r="O20">
+        <v>129</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>286</v>
+      </c>
+      <c r="S20">
+        <v>12291</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>2174</v>
+      </c>
+      <c r="V20">
+        <v>3456</v>
+      </c>
+      <c r="W20">
+        <v>3153</v>
+      </c>
+      <c r="X20">
+        <v>760</v>
+      </c>
+      <c r="Y20">
+        <v>2</v>
+      </c>
+      <c r="Z20">
+        <v>3866</v>
+      </c>
+      <c r="AA20">
+        <v>403</v>
+      </c>
+      <c r="AB20">
+        <v>110</v>
+      </c>
+      <c r="AC20">
+        <v>2</v>
+      </c>
+      <c r="AD20">
+        <v>205</v>
+      </c>
+      <c r="AE20">
+        <v>2880</v>
+      </c>
+      <c r="AF20">
+        <v>1873</v>
+      </c>
+      <c r="AG20">
+        <v>1797</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>2</v>
+      </c>
+      <c r="AK20">
+        <v>15983</v>
+      </c>
+      <c r="AL20">
+        <v>279</v>
+      </c>
+      <c r="AM20">
+        <v>82</v>
+      </c>
+      <c r="AN20">
+        <v>48</v>
+      </c>
+      <c r="AO20">
+        <v>2</v>
+      </c>
+      <c r="AP20">
+        <v>4961</v>
+      </c>
+      <c r="AQ20">
+        <v>283</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>15281</v>
+      </c>
+      <c r="AT20">
+        <v>129</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>2</v>
+      </c>
+      <c r="AX20">
+        <v>2</v>
+      </c>
+      <c r="AY20">
+        <v>2072</v>
+      </c>
+      <c r="AZ20">
+        <v>60</v>
+      </c>
+      <c r="BA20">
+        <v>24</v>
+      </c>
+      <c r="BB20">
+        <v>102</v>
+      </c>
+      <c r="BC20">
+        <v>38</v>
+      </c>
+      <c r="BD20">
+        <v>21</v>
+      </c>
+      <c r="BE20">
+        <v>1</v>
+      </c>
+      <c r="BF20">
+        <v>6</v>
+      </c>
+      <c r="BG20">
+        <v>4</v>
+      </c>
+      <c r="BH20">
+        <v>11</v>
+      </c>
+      <c r="BI20">
+        <v>1</v>
+      </c>
+      <c r="BJ20">
+        <v>45</v>
+      </c>
+      <c r="BK20">
+        <v>2050</v>
+      </c>
+      <c r="BL20">
+        <v>59</v>
+      </c>
+      <c r="BM20">
+        <v>19</v>
+      </c>
+      <c r="BN20">
+        <v>97</v>
+      </c>
+      <c r="BO20">
+        <v>38</v>
+      </c>
+      <c r="BP20">
+        <v>21</v>
+      </c>
+      <c r="BQ20">
+        <v>1</v>
+      </c>
+      <c r="BR20">
+        <v>6</v>
+      </c>
+      <c r="BS20">
+        <v>4</v>
+      </c>
+      <c r="BT20">
+        <v>11</v>
+      </c>
+      <c r="BU20">
+        <v>1</v>
+      </c>
+      <c r="BV20">
+        <v>45</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>388</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>389</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>21</v>
+      </c>
+      <c r="D22">
+        <v>22</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+      <c r="F22">
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>9</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>8</v>
+      </c>
+      <c r="M22">
+        <v>7</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22">
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>285</v>
+      </c>
+      <c r="S22">
+        <v>11642</v>
+      </c>
+      <c r="T22">
+        <v>3</v>
+      </c>
+      <c r="U22">
+        <v>1989</v>
+      </c>
+      <c r="V22">
+        <v>3059</v>
+      </c>
+      <c r="W22">
+        <v>730</v>
+      </c>
+      <c r="X22">
+        <v>229</v>
+      </c>
+      <c r="Y22">
+        <v>3</v>
+      </c>
+      <c r="Z22">
+        <v>859</v>
+      </c>
+      <c r="AA22">
+        <v>345</v>
+      </c>
+      <c r="AB22">
+        <v>111</v>
+      </c>
+      <c r="AC22">
+        <v>3</v>
+      </c>
+      <c r="AD22">
+        <v>176</v>
+      </c>
+      <c r="AE22">
+        <v>2614</v>
+      </c>
+      <c r="AF22">
+        <v>1592</v>
+      </c>
+      <c r="AG22">
+        <v>1524</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="AJ22">
+        <v>3</v>
+      </c>
+      <c r="AK22">
+        <v>16940</v>
+      </c>
+      <c r="AL22">
+        <v>278</v>
+      </c>
+      <c r="AM22">
+        <v>75</v>
+      </c>
+      <c r="AN22">
+        <v>48</v>
+      </c>
+      <c r="AO22">
+        <v>3</v>
+      </c>
+      <c r="AP22">
+        <v>4041</v>
+      </c>
+      <c r="AQ22">
+        <v>282</v>
+      </c>
+      <c r="AR22">
+        <v>1</v>
+      </c>
+      <c r="AS22">
+        <v>15730</v>
+      </c>
+      <c r="AT22">
+        <v>129</v>
+      </c>
+      <c r="AU22">
+        <v>1</v>
+      </c>
+      <c r="AV22">
+        <v>5</v>
+      </c>
+      <c r="AW22">
+        <v>2</v>
+      </c>
+      <c r="AX22">
+        <v>2</v>
+      </c>
+      <c r="AY22">
+        <v>27</v>
+      </c>
+      <c r="AZ22">
+        <v>7</v>
+      </c>
+      <c r="BA22">
+        <v>9</v>
+      </c>
+      <c r="BB22">
+        <v>17</v>
+      </c>
+      <c r="BC22">
+        <v>2</v>
+      </c>
+      <c r="BD22">
+        <v>3</v>
+      </c>
+      <c r="BE22">
+        <v>2</v>
+      </c>
+      <c r="BF22">
+        <v>3</v>
+      </c>
+      <c r="BG22">
+        <v>2</v>
+      </c>
+      <c r="BH22">
+        <v>3</v>
+      </c>
+      <c r="BI22">
+        <v>2</v>
+      </c>
+      <c r="BJ22">
+        <v>5</v>
+      </c>
+      <c r="BK22">
+        <v>6</v>
+      </c>
+      <c r="BL22">
+        <v>6</v>
+      </c>
+      <c r="BM22">
+        <v>4</v>
+      </c>
+      <c r="BN22">
+        <v>9</v>
+      </c>
+      <c r="BO22">
+        <v>2</v>
+      </c>
+      <c r="BP22">
+        <v>3</v>
+      </c>
+      <c r="BQ22">
+        <v>2</v>
+      </c>
+      <c r="BR22">
+        <v>3</v>
+      </c>
+      <c r="BS22">
+        <v>2</v>
+      </c>
+      <c r="BT22">
+        <v>3</v>
+      </c>
+      <c r="BU22">
+        <v>2</v>
+      </c>
+      <c r="BV22">
+        <v>5</v>
+      </c>
+      <c r="BW22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>390</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>99</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24">
+        <v>37921</v>
+      </c>
+      <c r="C24">
+        <v>72452</v>
+      </c>
+      <c r="D24">
+        <v>71059</v>
+      </c>
+      <c r="E24">
+        <v>71059</v>
+      </c>
+      <c r="F24">
+        <v>65013</v>
+      </c>
+      <c r="G24">
+        <v>75152</v>
+      </c>
+      <c r="H24">
+        <v>75737</v>
+      </c>
+      <c r="I24">
+        <v>65398</v>
+      </c>
+      <c r="J24">
+        <v>76020</v>
+      </c>
+      <c r="K24">
+        <v>75737</v>
+      </c>
+      <c r="L24">
+        <v>70242</v>
+      </c>
+      <c r="M24">
+        <v>52064</v>
+      </c>
+      <c r="N24">
+        <v>75877</v>
+      </c>
+      <c r="O24">
+        <v>75891</v>
+      </c>
+      <c r="P24">
+        <v>76020</v>
+      </c>
+      <c r="Q24">
+        <v>76020</v>
+      </c>
+      <c r="R24">
+        <v>75734</v>
+      </c>
+      <c r="S24">
+        <v>25561</v>
+      </c>
+      <c r="T24">
+        <v>76018</v>
+      </c>
+      <c r="U24">
+        <v>73846</v>
+      </c>
+      <c r="V24">
+        <v>72564</v>
+      </c>
+      <c r="W24">
+        <v>72867</v>
+      </c>
+      <c r="X24">
+        <v>75260</v>
+      </c>
+      <c r="Y24">
+        <v>76018</v>
+      </c>
+      <c r="Z24">
+        <v>72154</v>
+      </c>
+      <c r="AA24">
+        <v>75617</v>
+      </c>
+      <c r="AB24">
+        <v>75910</v>
+      </c>
+      <c r="AC24">
+        <v>76018</v>
+      </c>
+      <c r="AD24">
+        <v>75815</v>
+      </c>
+      <c r="AE24">
+        <v>73140</v>
+      </c>
+      <c r="AF24">
+        <v>74147</v>
+      </c>
+      <c r="AG24">
+        <v>74223</v>
+      </c>
+      <c r="AH24">
+        <v>76020</v>
+      </c>
+      <c r="AI24">
+        <v>76020</v>
+      </c>
+      <c r="AJ24">
+        <v>76018</v>
+      </c>
+      <c r="AK24">
+        <v>20310</v>
+      </c>
+      <c r="AL24">
+        <v>75741</v>
+      </c>
+      <c r="AM24">
+        <v>75938</v>
+      </c>
+      <c r="AN24">
+        <v>75972</v>
+      </c>
+      <c r="AO24">
+        <v>76018</v>
+      </c>
+      <c r="AP24">
+        <v>71059</v>
+      </c>
+      <c r="AQ24">
+        <v>75737</v>
+      </c>
+      <c r="AR24">
+        <v>76020</v>
+      </c>
+      <c r="AS24">
+        <v>21786</v>
+      </c>
+      <c r="AT24">
+        <v>75891</v>
+      </c>
+      <c r="AU24">
+        <v>76020</v>
+      </c>
+      <c r="AV24">
+        <v>30064</v>
+      </c>
+      <c r="AW24">
+        <v>76018</v>
+      </c>
+      <c r="AX24">
+        <v>76018</v>
+      </c>
+      <c r="AY24">
+        <v>73948</v>
+      </c>
+      <c r="AZ24">
+        <v>75960</v>
+      </c>
+      <c r="BA24">
+        <v>75996</v>
+      </c>
+      <c r="BB24">
+        <v>75918</v>
+      </c>
+      <c r="BC24">
+        <v>75982</v>
+      </c>
+      <c r="BD24">
+        <v>75999</v>
+      </c>
+      <c r="BE24">
+        <v>76019</v>
+      </c>
+      <c r="BF24">
+        <v>76014</v>
+      </c>
+      <c r="BG24">
+        <v>76016</v>
+      </c>
+      <c r="BH24">
+        <v>76009</v>
+      </c>
+      <c r="BI24">
+        <v>76019</v>
+      </c>
+      <c r="BJ24">
+        <v>75975</v>
+      </c>
+      <c r="BK24">
+        <v>73970</v>
+      </c>
+      <c r="BL24">
+        <v>75961</v>
+      </c>
+      <c r="BM24">
+        <v>76001</v>
+      </c>
+      <c r="BN24">
+        <v>75923</v>
+      </c>
+      <c r="BO24">
+        <v>75982</v>
+      </c>
+      <c r="BP24">
+        <v>75999</v>
+      </c>
+      <c r="BQ24">
+        <v>76019</v>
+      </c>
+      <c r="BR24">
+        <v>76014</v>
+      </c>
+      <c r="BS24">
+        <v>76016</v>
+      </c>
+      <c r="BT24">
+        <v>76009</v>
+      </c>
+      <c r="BU24">
+        <v>76019</v>
+      </c>
+      <c r="BV24">
+        <v>75975</v>
+      </c>
+      <c r="BW24">
+        <v>76020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.49880000000000002</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.95309999999999995</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0.98860000000000003</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0.86029999999999995</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="L25" s="9">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="M25" s="9">
+        <v>0.68489999999999995</v>
+      </c>
+      <c r="N25" s="9">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="O25" s="9">
+        <v>0.99829999999999997</v>
+      </c>
+      <c r="P25" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>1</v>
+      </c>
+      <c r="R25" s="9">
+        <v>0.99619999999999997</v>
+      </c>
+      <c r="S25" s="9">
+        <v>0.3362</v>
+      </c>
+      <c r="T25" s="9">
+        <v>1</v>
+      </c>
+      <c r="U25" s="9">
+        <v>0.97140000000000004</v>
+      </c>
+      <c r="V25" s="9">
+        <v>0.95450000000000002</v>
+      </c>
+      <c r="W25" s="9">
+        <v>0.95850000000000002</v>
+      </c>
+      <c r="X25" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="Y25" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="9">
+        <v>0.94910000000000005</v>
+      </c>
+      <c r="AA25" s="9">
+        <v>0.99470000000000003</v>
+      </c>
+      <c r="AB25" s="9">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="AC25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="9">
+        <v>0.99729999999999996</v>
+      </c>
+      <c r="AE25" s="9">
+        <v>0.96209999999999996</v>
+      </c>
+      <c r="AF25" s="9">
+        <v>0.97540000000000004</v>
+      </c>
+      <c r="AG25" s="9">
+        <v>0.97640000000000005</v>
+      </c>
+      <c r="AH25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AK25" s="9">
+        <v>0.26719999999999999</v>
+      </c>
+      <c r="AL25" s="9">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="AM25" s="9">
+        <v>0.99890000000000001</v>
+      </c>
+      <c r="AN25" s="9">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="AO25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="9">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="AQ25" s="9">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="AR25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AS25" s="9">
+        <v>0.28660000000000002</v>
+      </c>
+      <c r="AT25" s="9">
+        <v>0.99829999999999997</v>
+      </c>
+      <c r="AU25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV25" s="9">
+        <v>0.39550000000000002</v>
+      </c>
+      <c r="AW25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AX25" s="9">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="9">
+        <v>0.97270000000000001</v>
+      </c>
+      <c r="AZ25" s="9">
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="BA25" s="9">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="BB25" s="9">
+        <v>0.99870000000000003</v>
+      </c>
+      <c r="BC25" s="9">
+        <v>0.99950000000000006</v>
+      </c>
+      <c r="BD25" s="9">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="BE25" s="9">
+        <v>1</v>
+      </c>
+      <c r="BF25" s="9">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BG25" s="9">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BH25" s="9">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BI25" s="9">
+        <v>1</v>
+      </c>
+      <c r="BJ25" s="9">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="BK25" s="9">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="BL25" s="9">
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="BM25" s="9">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="BN25" s="9">
+        <v>0.99870000000000003</v>
+      </c>
+      <c r="BO25" s="9">
+        <v>0.99950000000000006</v>
+      </c>
+      <c r="BP25" s="9">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="BQ25" s="9">
+        <v>1</v>
+      </c>
+      <c r="BR25" s="9">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BS25" s="9">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BT25" s="9">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BU25" s="9">
+        <v>1</v>
+      </c>
+      <c r="BV25" s="9">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="BW25" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>393</v>
+      </c>
+      <c r="B26">
+        <v>19528</v>
+      </c>
+      <c r="C26">
+        <v>72452</v>
+      </c>
+      <c r="D26">
+        <v>71059</v>
+      </c>
+      <c r="E26">
+        <v>71059</v>
+      </c>
+      <c r="F26">
+        <v>9065</v>
+      </c>
+      <c r="G26">
+        <v>75152</v>
+      </c>
+      <c r="H26">
+        <v>75737</v>
+      </c>
+      <c r="I26">
+        <v>9177</v>
+      </c>
+      <c r="J26">
+        <v>76020</v>
+      </c>
+      <c r="K26">
+        <v>75737</v>
+      </c>
+      <c r="L26">
+        <v>436</v>
+      </c>
+      <c r="M26">
+        <v>21908</v>
+      </c>
+      <c r="N26">
+        <v>75877</v>
+      </c>
+      <c r="O26">
+        <v>75891</v>
+      </c>
+      <c r="P26">
+        <v>76020</v>
+      </c>
+      <c r="Q26">
+        <v>76020</v>
+      </c>
+      <c r="R26">
+        <v>75734</v>
+      </c>
+      <c r="S26">
+        <v>25561</v>
+      </c>
+      <c r="T26">
+        <v>76018</v>
+      </c>
+      <c r="U26">
+        <v>73846</v>
+      </c>
+      <c r="V26">
+        <v>72564</v>
+      </c>
+      <c r="W26">
+        <v>72867</v>
+      </c>
+      <c r="X26">
+        <v>75260</v>
+      </c>
+      <c r="Y26">
+        <v>76018</v>
+      </c>
+      <c r="Z26">
+        <v>72154</v>
+      </c>
+      <c r="AA26">
+        <v>75617</v>
+      </c>
+      <c r="AB26">
+        <v>75910</v>
+      </c>
+      <c r="AC26">
+        <v>76018</v>
+      </c>
+      <c r="AD26">
+        <v>75815</v>
+      </c>
+      <c r="AE26">
+        <v>73140</v>
+      </c>
+      <c r="AF26">
+        <v>74147</v>
+      </c>
+      <c r="AG26">
+        <v>74223</v>
+      </c>
+      <c r="AH26">
+        <v>76020</v>
+      </c>
+      <c r="AI26">
+        <v>76020</v>
+      </c>
+      <c r="AJ26">
+        <v>76018</v>
+      </c>
+      <c r="AK26">
+        <v>20310</v>
+      </c>
+      <c r="AL26">
+        <v>75741</v>
+      </c>
+      <c r="AM26">
+        <v>75938</v>
+      </c>
+      <c r="AN26">
+        <v>75972</v>
+      </c>
+      <c r="AO26">
+        <v>76018</v>
+      </c>
+      <c r="AP26">
+        <v>71059</v>
+      </c>
+      <c r="AQ26">
+        <v>75737</v>
+      </c>
+      <c r="AR26">
+        <v>76020</v>
+      </c>
+      <c r="AS26">
+        <v>21786</v>
+      </c>
+      <c r="AT26">
+        <v>75891</v>
+      </c>
+      <c r="AU26">
+        <v>76020</v>
+      </c>
+      <c r="AV26">
+        <v>411</v>
+      </c>
+      <c r="AW26">
+        <v>76018</v>
+      </c>
+      <c r="AX26">
+        <v>76018</v>
+      </c>
+      <c r="AY26">
+        <v>73948</v>
+      </c>
+      <c r="AZ26">
+        <v>75960</v>
+      </c>
+      <c r="BA26">
+        <v>75996</v>
+      </c>
+      <c r="BB26">
+        <v>75918</v>
+      </c>
+      <c r="BC26">
+        <v>75982</v>
+      </c>
+      <c r="BD26">
+        <v>75999</v>
+      </c>
+      <c r="BE26">
+        <v>76019</v>
+      </c>
+      <c r="BF26">
+        <v>76014</v>
+      </c>
+      <c r="BG26">
+        <v>76016</v>
+      </c>
+      <c r="BH26">
+        <v>76009</v>
+      </c>
+      <c r="BI26">
+        <v>76019</v>
+      </c>
+      <c r="BJ26">
+        <v>75975</v>
+      </c>
+      <c r="BK26">
+        <v>73970</v>
+      </c>
+      <c r="BL26">
+        <v>75961</v>
+      </c>
+      <c r="BM26">
+        <v>76001</v>
+      </c>
+      <c r="BN26">
+        <v>75923</v>
+      </c>
+      <c r="BO26">
+        <v>75982</v>
+      </c>
+      <c r="BP26">
+        <v>75999</v>
+      </c>
+      <c r="BQ26">
+        <v>76019</v>
+      </c>
+      <c r="BR26">
+        <v>76014</v>
+      </c>
+      <c r="BS26">
+        <v>76016</v>
+      </c>
+      <c r="BT26">
+        <v>76009</v>
+      </c>
+      <c r="BU26">
+        <v>76019</v>
+      </c>
+      <c r="BV26">
+        <v>75975</v>
+      </c>
+      <c r="BW26">
+        <v>76020</v>
+      </c>
+    </row>
+    <row r="27" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>394</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.25690000000000002</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0.95309999999999995</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0.1192</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0.98860000000000003</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0.1207</v>
+      </c>
+      <c r="J27" s="10">
+        <v>1</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="L27" s="9">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0.28820000000000001</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="O27" s="10">
+        <v>0.99829999999999997</v>
+      </c>
+      <c r="P27" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>1</v>
+      </c>
+      <c r="R27" s="10">
+        <v>0.99619999999999997</v>
+      </c>
+      <c r="S27" s="9">
+        <v>0.3362</v>
+      </c>
+      <c r="T27" s="10">
+        <v>1</v>
+      </c>
+      <c r="U27" s="10">
+        <v>0.97140000000000004</v>
+      </c>
+      <c r="V27" s="10">
+        <v>0.95450000000000002</v>
+      </c>
+      <c r="W27" s="10">
+        <v>0.95850000000000002</v>
+      </c>
+      <c r="X27" s="10">
+        <v>0.99</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>0.94910000000000005</v>
+      </c>
+      <c r="AA27" s="10">
+        <v>0.99470000000000003</v>
+      </c>
+      <c r="AB27" s="10">
+        <v>0.99860000000000004</v>
+      </c>
+      <c r="AC27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="10">
+        <v>0.99729999999999996</v>
+      </c>
+      <c r="AE27" s="10">
+        <v>0.96209999999999996</v>
+      </c>
+      <c r="AF27" s="10">
+        <v>0.97540000000000004</v>
+      </c>
+      <c r="AG27" s="10">
+        <v>0.97640000000000005</v>
+      </c>
+      <c r="AH27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AJ27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="9">
+        <v>0.26719999999999999</v>
+      </c>
+      <c r="AL27" s="10">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="AM27" s="10">
+        <v>0.99890000000000001</v>
+      </c>
+      <c r="AN27" s="10">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="AO27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AP27" s="10">
+        <v>0.93469999999999998</v>
+      </c>
+      <c r="AQ27" s="10">
+        <v>0.99629999999999996</v>
+      </c>
+      <c r="AR27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS27" s="9">
+        <v>0.28660000000000002</v>
+      </c>
+      <c r="AT27" s="10">
+        <v>0.99829999999999997</v>
+      </c>
+      <c r="AU27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV27" s="9">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="AW27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY27" s="10">
+        <v>0.97270000000000001</v>
+      </c>
+      <c r="AZ27" s="10">
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="BA27" s="10">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="BB27" s="10">
+        <v>0.99870000000000003</v>
+      </c>
+      <c r="BC27" s="10">
+        <v>0.99950000000000006</v>
+      </c>
+      <c r="BD27" s="10">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="BE27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BF27" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BG27" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BH27" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BI27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BJ27" s="10">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="BK27" s="10">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="BL27" s="10">
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="BM27" s="10">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="BN27" s="10">
+        <v>0.99870000000000003</v>
+      </c>
+      <c r="BO27" s="10">
+        <v>0.99950000000000006</v>
+      </c>
+      <c r="BP27" s="10">
+        <v>0.99970000000000003</v>
+      </c>
+      <c r="BQ27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BR27" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BS27" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BT27" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="BU27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BV27" s="10">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="BW27" s="10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
